--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486409_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486409_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.966799999999999</v>
+        <v>10.7606</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5523</v>
+        <v>12.2228</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5855</v>
+        <v>-1.4622</v>
       </c>
       <c r="G2" t="n">
         <v>7.7187</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2469</v>
+        <v>-0.453</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.822</v>
+        <v>-0.1514</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4249</v>
+        <v>-0.3016</v>
       </c>
       <c r="V2" t="n">
         <v>1.9724</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1205</v>
+        <v>4.2071</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1015</v>
+        <v>2.0957</v>
       </c>
       <c r="F3" t="n">
-        <v>2.019</v>
+        <v>2.1114</v>
       </c>
       <c r="G3" t="n">
         <v>0.7796999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5397</v>
+        <v>0.6264</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6872</v>
+        <v>0.6814</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1475</v>
+        <v>-0.055</v>
       </c>
       <c r="V3" t="n">
         <v>1.931</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0482</v>
+        <v>2.5589</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0839</v>
+        <v>1.7487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9643</v>
+        <v>0.8102</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8491</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6183</v>
+        <v>0.1289</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7367</v>
+        <v>0.4014</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1184</v>
+        <v>-0.2725</v>
       </c>
       <c r="V4" t="n">
         <v>2.3215</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6306</v>
+        <v>1.0814</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3017</v>
+        <v>3.4134</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6711</v>
+        <v>-2.3321</v>
       </c>
       <c r="G5" t="n">
         <v>0.0014</v>
@@ -844,13 +844,13 @@
         <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4589</v>
+        <v>-0.0081</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0601</v>
+        <v>0.1719</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.519</v>
+        <v>-0.18</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3045</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.23</v>
+        <v>-0.1554</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4893</v>
+        <v>0.0423</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2593</v>
+        <v>-0.1977</v>
       </c>
       <c r="G6" t="n">
         <v>0.0158</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2141</v>
+        <v>-0.1712</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4711</v>
+        <v>0.024</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.847</v>
+        <v>-0.6902</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.882</v>
+        <v>0.1661</v>
       </c>
       <c r="F7" t="n">
-        <v>0.035</v>
+        <v>-0.8563</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6726</v>
+        <v>1.0433</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6726</v>
+        <v>-0.9337</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.977</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4901</v>
+        <v>2.83</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4901</v>
+        <v>-0.6324</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.4624</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1825</v>
+        <v>-1.7867</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1825</v>
+        <v>-0.3013</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.4854</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6081</v>
+        <v>0.2941</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6081</v>
+        <v>0.1658</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1283</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2875</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.808</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.38</v>
+        <v>-1.2941</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6162</v>
+        <v>-1.3291</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7638</v>
+        <v>0.035</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0433</v>
+        <v>-1.6726</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9337</v>
+        <v>-1.6726</v>
       </c>
       <c r="I8" t="n">
-        <v>1.977</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.83</v>
+        <v>-1.4901</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6324</v>
+        <v>-1.4901</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4624</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7867</v>
+        <v>-0.1825</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3013</v>
+        <v>-0.1825</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4854</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6101</v>
+        <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3957</v>
+        <v>0.161</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6165</v>
+        <v>0.161</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2207</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2875</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2664</v>
+        <v>-2.2207</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1187</v>
+        <v>-1.9917</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1477</v>
+        <v>-0.2291</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4295</v>
+        <v>-1.7667</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1801</v>
+        <v>-0.6113</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2494</v>
+        <v>-1.1555</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6118</v>
+        <v>-1.2279</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1672</v>
+        <v>-0.5594</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5554</v>
+        <v>-0.6686</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8178</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0129</v>
+        <v>-0.0519</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.4869</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4061</v>
+        <v>-0.1712</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6682</v>
+        <v>0.1286</v>
       </c>
       <c r="U9" t="n">
-        <v>0.738</v>
+        <v>-0.2998</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.243</v>
+        <v>0.3698</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.243</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2824</v>
+        <v>-2.5438</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9917</v>
+        <v>-2.1187</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2907</v>
+        <v>-0.4251</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7667</v>
+        <v>-2.4295</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6113</v>
+        <v>-2.1801</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1555</v>
+        <v>-0.2494</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2279</v>
+        <v>-0.6118</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5594</v>
+        <v>-1.1672</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6686</v>
+        <v>0.5554</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-1.8178</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0519</v>
+        <v>-1.0129</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4869</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2329</v>
+        <v>1.1287</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1286</v>
+        <v>0.6682</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3615</v>
+        <v>0.4605</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3698</v>
+        <v>-1.243</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1745</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8691</v>
+        <v>-3.607</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6719</v>
+        <v>-2.2249</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1972</v>
+        <v>-1.3821</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0883</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4333</v>
+        <v>-0.1712</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1146</v>
+        <v>-0.0703</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9015</v>
+        <v>-4.6471</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8636</v>
+        <v>-2.6401</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0379</v>
+        <v>-2.007</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9955</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4709</v>
+        <v>-0.2166</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.449699999999998</v>
+        <v>3.449700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>9.384600000000001</v>
+        <v>9.384500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.9349</v>
+        <v>-5.935</v>
       </c>
       <c r="G13" t="n">
         <v>-5.2428</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1506999999999985</v>
+        <v>-0.1506999999999994</v>
       </c>
       <c r="I13" t="n">
         <v>-5.0921</v>
@@ -1447,7 +1447,7 @@
         <v>4.595300000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>4.769200000000001</v>
+        <v>4.7692</v>
       </c>
       <c r="M13" t="n">
         <v>-14.6076</v>
@@ -1468,13 +1468,13 @@
         <v>14.138</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1477</v>
+        <v>1.1478</v>
       </c>
       <c r="T13" t="n">
-        <v>2.031000000000001</v>
+        <v>2.031</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8834</v>
+        <v>-0.8833</v>
       </c>
       <c r="V13" t="n">
         <v>3.1947</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.77</v>
+        <v>6.2691</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6774</v>
+        <v>6.4539</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0926</v>
+        <v>-0.1848</v>
       </c>
       <c r="G14" t="n">
         <v>5.5952</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.4341</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5997</v>
+        <v>0.3761</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3354</v>
+        <v>0.058</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1952</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.408</v>
+        <v>2.9436</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1785</v>
+        <v>4.8374</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7705</v>
+        <v>-1.8938</v>
       </c>
       <c r="G15" t="n">
         <v>2.0528</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4644</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7557</v>
+        <v>0.4146</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2913</v>
+        <v>-0.4146</v>
       </c>
       <c r="V15" t="n">
         <v>0.0207</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2787</v>
+        <v>1.9107</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8334</v>
+        <v>1.2804</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4454</v>
+        <v>0.6303</v>
       </c>
       <c r="G16" t="n">
         <v>3.3463</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4798</v>
+        <v>-0.8478</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="V16" t="n">
         <v>0.9347</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8118</v>
+        <v>1.3513</v>
       </c>
       <c r="E17" t="n">
-        <v>1.321</v>
+        <v>1.7681</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5092</v>
+        <v>-0.4168</v>
       </c>
       <c r="G17" t="n">
         <v>-0.414</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5344</v>
+        <v>0.0051</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3425</v>
+        <v>0.1046</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1919</v>
+        <v>-0.0994</v>
       </c>
       <c r="V17" t="n">
         <v>1.3252</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3127</v>
+        <v>0.9562</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4432</v>
+        <v>-0.1079</v>
       </c>
       <c r="F18" t="n">
-        <v>0.756</v>
+        <v>1.0642</v>
       </c>
       <c r="G18" t="n">
         <v>0.6108</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.733</v>
+        <v>-0.0895</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3425</v>
+        <v>-0.0072</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3906</v>
+        <v>-0.0823</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1127</v>
+        <v>0.0569</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9644</v>
+        <v>-0.5174</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8517</v>
+        <v>0.5743</v>
       </c>
       <c r="G19" t="n">
         <v>0.5913</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2691</v>
+        <v>-0.0994</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.411</v>
+        <v>0.0361</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1419</v>
+        <v>-0.1355</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1937</v>
+        <v>-2.15</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4334</v>
+        <v>-1.1537</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7603</v>
+        <v>-0.9963</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1846</v>
+        <v>-2.7979</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1033</v>
+        <v>-0.8488</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0813</v>
+        <v>-1.9491</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6678</v>
+        <v>-0.0517</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8646</v>
+        <v>0.73</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8032</v>
+        <v>-0.7817</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4832</v>
+        <v>-2.7462</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7613</v>
+        <v>-1.5788</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2781</v>
+        <v>-1.1674</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.4801</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1665</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6187</v>
+        <v>-0.0144</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5478</v>
+        <v>-0.5345</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0647</v>
+        <v>0.5443</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.695</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0363</v>
+        <v>-3.5385</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8242</v>
+        <v>-1.4392</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2121</v>
+        <v>-2.0993</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7979</v>
+        <v>1.1846</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8488</v>
+        <v>0.1033</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9491</v>
+        <v>1.0813</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0517</v>
+        <v>2.6678</v>
       </c>
       <c r="K21" t="n">
-        <v>0.73</v>
+        <v>1.8646</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7817</v>
+        <v>0.8032</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7462</v>
+        <v>-1.4832</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5788</v>
+        <v>-1.7613</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1674</v>
+        <v>0.2781</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4352</v>
+        <v>0.8217</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.6129</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7502</v>
+        <v>0.2088</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5443</v>
+        <v>-2.0647</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X21" t="n">
-        <v>0.5443</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1108</v>
+        <v>-5.1301</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4698</v>
+        <v>-2.5815</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.641</v>
+        <v>-2.5486</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3302</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1542</v>
+        <v>0.1349</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1971</v>
+        <v>0.0853</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0429</v>
+        <v>0.0496</v>
       </c>
       <c r="V22" t="n">
         <v>-2.6297</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5774</v>
+        <v>-6.1189</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9404</v>
+        <v>-2.6051</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6371</v>
+        <v>-3.5138</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5961</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4163</v>
+        <v>-0.9577</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6629</v>
+        <v>-0.5396</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.449699999999998</v>
+        <v>-3.449699999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>5.934899999999995</v>
+        <v>5.935</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.384499999999999</v>
+        <v>-9.384599999999999</v>
       </c>
       <c r="G24" t="n">
         <v>5.242800000000001</v>
@@ -2326,13 +2326,13 @@
         <v>9.787699999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.147699999999999</v>
+        <v>-1.1475</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8831999999999999</v>
+        <v>0.8833999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.031</v>
+        <v>-2.0309</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1947</v>
